--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_962_Spain_mainland_Med_and_Gulf_of_Cadiz.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_962_Spain_mainland_Med_and_Gulf_of_Cadiz.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R44e974817aaf4747"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R121f465e052145d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re44ff9d881f44bb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd3029299506a48eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R776eea8e1a254a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra0775092eaff4dac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re3feb706c2484e53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R39c330455cae4da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re3e61ad40027474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4f713b9133a54f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6ccf65e4474f4297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5e366e814d8d46cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ962CommercialTable" displayName="EEZ962CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ962CommercialTable" displayName="EEZ962CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ962FunctionalTable" displayName="EEZ962FunctionalTable" ref="A1:O27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O27"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ962FunctionalTable" displayName="EEZ962FunctionalTable" ref="A1:E27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E27"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ962ValidationTable" displayName="EEZ962ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ962ValidationTable" displayName="EEZ962ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -25819,7 +25773,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d8e128e276641af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaa0232f252446bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25829,20 +25783,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -25850,714 +25794,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>37663.9962414135</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>37663.9962414135</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$376,A2,'Species'!$U$2:$U$376))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4852062.627297281</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>4852062.627297281</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8929.392409867502</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.2213481036890865</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1664.746473910737</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8929.392409867502</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1896.3795032681696</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$376,A3,'Species'!$U$2:$U$376))</x:f>
-        <x:v>16933516.742711097</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.2213481036890865</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1664.746473910737</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>14865174.528492222</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2068342.2142188754</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1391401231283538</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.13914012312835375</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>12359.532361244903</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.254381133859064</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>179.63093640826884</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>12359.532361244903</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>215.24978060362602</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$376,A4,'Species'!$U$2:$U$376))</x:f>
-        <x:v>2660386.6291213813</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.254381133859064</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>179.63093640826884</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2220154.371618724</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>440232.25750265736</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1982890303171496</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.1982890303171496</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1721.6899969467997</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6466528341862268</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>443.25417427038394</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1721.6899969467997</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>604.0527860931153</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$376,A5,'Species'!$U$2:$U$376))</x:f>
-        <x:v>1039991.6394443614</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6466528341862268</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>443.25417427038394</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>763146.2779462335</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>276845.3614981279</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.362768409541575</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3627684095415751</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>21878.6922732003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.131941887103302</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>135.5008086737168</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>21878.6922732003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>143.69590188558442</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$376,A6,'Species'!$U$2:$U$376))</x:f>
-        <x:v>3143878.4182746843</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.131941887103302</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>135.5008086737168</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2964580.4957420398</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>179297.9225326446</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0604800317583436</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.06048003175834361</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1913.1323869670002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.228262018401765</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>16.914611156191086</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1913.1323869670002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>29.119455431139123</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$376,A7,'Species'!$U$2:$U$376))</x:f>
-        <x:v>55709.37327615437</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.228262018401765</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>16.914611156191086</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>32359.890415862505</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>23349.482860291868</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7215563019597302</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7215563019597303</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>30678.223666201407</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.576607106817769</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>377.2307671584901</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>30678.223666201407</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>710.4145799935933</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$376,A8,'Species'!$U$2:$U$376))</x:f>
-        <x:v>21794257.380773988</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.576607106817769</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>377.2307671584901</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>11572769.848660903</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>10221487.532113085</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8832360502957572</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8832360502957572</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>57029.024177274696</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.7314672906836956</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>538.8492598826352</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>57029.024177274696</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>858.9429431296492</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$376,A9,'Species'!$U$2:$U$376))</x:f>
-        <x:v>48984677.87064025</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.7314672906836956</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>538.8492598826352</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>30730047.46975338</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>18254630.400886867</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5940319623278918</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5940319623278918</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>112.19537917240001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6055096565270492</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>403.18991126149</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>112.19537917240001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>406.51161781833076</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$376,A10,'Species'!$U$2:$U$376))</x:f>
-        <x:v>45608.72509911338</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6055096565270492</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>403.18991126149</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>45236.044972469186</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>372.68012664419075</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.008238565658669</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.008238565658668992</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1869.7674859862</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7205878246774122</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>525.5182766646116</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1869.7674859862</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>605.2867634121502</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$376,A11,'Species'!$U$2:$U$376))</x:f>
-        <x:v>1131745.50992586</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7205878246774122</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>525.5182766646116</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>982596.9869989911</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>149148.52292686887</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1517901285066956</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.1517901285066957</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>18237.707346765197</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.307181955458646</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2028.5324315348312</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>18237.707346765197</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2146.743242441066</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$376,A12,'Species'!$U$2:$U$376))</x:f>
-        <x:v>39151675.00428597</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.307181955458646</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2028.5324315348312</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>36995780.82975426</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>2155894.1745317057</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0582740552078793</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.058274055207879386</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>8274.4762623008</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.4006841646490304</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2515.8466436084054</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>8274.4762623008</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2603.7219133777335</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$376,A13,'Species'!$U$2:$U$376))</x:f>
-        <x:v>21544435.165876474</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.4006841646490304</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2515.8466436084054</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>20817313.33212689</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>727121.8337495849</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.034928706800384</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.03492870680038399</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c5a5baa1579404a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ce338d1f2934a00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26567,20 +26047,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -26588,1470 +26058,516 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>11621.914083307</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8482672353554728</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>705.1268227030502</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>11621.914083307</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>892.8662813147882</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$376,A2,'Species'!$U$2:$U$376))</x:f>
-        <x:v>10376815.209322287</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8482672353554728</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>705.1268227030502</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>8194923.3512900965</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2181891.8580321902</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2662492087480846</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.26624920874808466</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1412.8864063861997</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.331578918004016</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2145.7489960702223</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1412.8864063861997</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2316.618139290886</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$376,A3,'Species'!$U$2:$U$376))</x:f>
-        <x:v>3273118.2777917846</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.331578918004016</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2145.7489960702223</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3031699.588064452</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>241418.68972733244</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0796314683281212</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.07963146832812118</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>21.0519825709</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.139127300751075</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1377.6132168219908</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>21.0519825709</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1539.2307932897918</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$376,A4,'Species'!$U$2:$U$376))</x:f>
-        <x:v>32403.85983292928</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.139127300751075</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1377.6132168219908</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>29001.489429978035</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3402.3704029512446</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1173170919778455</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.11731709197784541</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4267.598494265299</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.235368105333291</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1719.3650930069614</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4267.598494265299</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2226.324523475397</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$376,A5,'Species'!$U$2:$U$376))</x:f>
-        <x:v>9501059.184129516</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.235368105333291</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1719.3650930069614</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7337559.882008825</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2163499.3021206902</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2948526944802776</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2948526944802776</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>8709.1981867549</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.166210267550869</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1466.2575708249349</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>8709.1981867549</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1805.4842990962431</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$376,A6,'Species'!$U$2:$U$376))</x:f>
-        <x:v>15724320.583903443</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.166210267550869</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1466.2575708249349</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>12769927.777144168</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2954392.8067592755</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2313554828436146</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.23135548284361465</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6.9313463133</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6.9313463133</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$376,A7,'Species'!$U$2:$U$376))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>15878.79705927014</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>15878.79705927014</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>8364.2860268065</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.443261256899767</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2774.9889423152777</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>8364.2860268065</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2812.9148014734797</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$376,A8,'Species'!$U$2:$U$376))</x:f>
-        <x:v>23528023.968561806</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.443261256899767</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2774.9889423152777</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>23210801.234750226</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>317222.73381157964</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0136670307329438</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.013667030732943732</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>90.6256936779</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.065478285699004</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1162.728414262018</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>90.6256936779</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1653.23302446462</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$376,A9,'Species'!$U$2:$U$376))</x:f>
-        <x:v>149825.38965331882</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.065478285699004</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1162.728414262018</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>105373.06910150006</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>44452.32055181876</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.421856560987137</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.421856560987137</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>761.4811576957001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.258405358069558</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1813.0315349944074</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>761.4811576957001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2198.601606749248</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$376,A10,'Species'!$U$2:$U$376))</x:f>
-        <x:v>1674193.6968190435</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.258405358069558</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1813.0315349944074</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1380589.3522063536</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>293604.3446126899</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2126659488887652</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.21266594888876525</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>16386.290920610598</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.357772427922245</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2279.14747647878</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>16386.290920610598</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2300.242750438105</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$376,A11,'Species'!$U$2:$U$376))</x:f>
-        <x:v>37692446.896704264</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.357772427922245</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2279.14747647878</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>37346773.60055679</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>345673.29614747316</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.009255774001916</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.009255774001915915</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2495.8565319968993</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.8966891231795158</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>78.82956375640357</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2495.8565319968993</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>97.75448682117587</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$376,A12,'Species'!$U$2:$U$376))</x:f>
-        <x:v>243981.1744646366</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.8966891231795158</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>78.82956375640357</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>196747.28161588588</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>47233.89284875072</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2400739286500868</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.2400739286500868</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1817.8326751684997</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.7365004357030007</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>545.1304425870647</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1817.8326751684997</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1011.7499640446529</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$376,A13,'Species'!$U$2:$U$376))</x:f>
-        <x:v>1839192.1437409248</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.7365004357030007</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>545.1304425870647</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>990955.9307638322</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>848236.2129770926</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.8559777348759285</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.8559777348759287</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>61.0634747958</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.828056606470286</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>673.0643785959196</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>61.0634747958</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>761.0421498125218</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$376,A14,'Species'!$U$2:$U$376))</x:f>
-        <x:v>46471.87813361837</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.828056606470286</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>673.0643785959196</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>41099.64971834273</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5372.22841527564</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1307122676736103</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.13071226767361038</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>15343.5005844606</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.6405039970176505</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>437.02270117884837</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>15343.5005844606</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>721.2445033187436</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$376,A15,'Species'!$U$2:$U$376))</x:f>
-        <x:v>11066415.458210137</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.6405039970176505</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>437.02270117884837</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>6705458.07096021</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>4360957.387249927</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.6503593551850284</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.6503593551850285</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>22195.1684702086</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.423265894719886</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>265.01221666410567</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>22195.1684702086</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>338.960599114715</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$376,A16,'Species'!$U$2:$U$376))</x:f>
-        <x:v>7523287.60211394</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.423265894719886</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>265.01221666410567</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>5881990.795523248</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1641296.8065906921</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2790376360058018</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.2790376360058017</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>26194.2099437701</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.8754456474890437</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>750.6641016666291</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>26194.2099437701</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>941.0645014957131</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$376,A17,'Species'!$U$2:$U$376))</x:f>
-        <x:v>24650441.12280806</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.8754456474890437</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>750.6641016666291</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>19663053.076307267</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>4987388.046500795</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2536426071346103</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.2536426071346103</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1803.6461408050998</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.2134757122777957</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>163.48417207904527</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1803.6461408050998</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>343.4937465017338</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$376,A18,'Species'!$U$2:$U$376))</x:f>
-        <x:v>619541.1702685375</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.2134757122777957</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>163.48417207904527</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>294867.59605308686</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>324673.5742154506</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>2.1010825826958537</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>1.1010825826958537</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>4468.204694366</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.3429279657547086</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>22.02561105001948</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>4468.204694366</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>27.828070808346823</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$376,A19,'Species'!$U$2:$U$376))</x:f>
-        <x:v>124341.51662100472</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.3429279657547086</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>22.02561105001948</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>98414.93868997668</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>25926.577931028034</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.2634414884177394</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.2634414884177395</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>9863.675829248</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3448897795964334</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>221.25331154539487</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>9863.675829248</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>244.98021797224553</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$376,A20,'Species'!$U$2:$U$376))</x:f>
-        <x:v>2416405.454656745</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3448897795964334</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>221.25331154539487</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>2182370.941231389</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>234034.51342535578</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.107238649948896</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.10723864994889608</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>410.3341699955</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.474821131090595</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>298.4153309761828</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>410.3341699955</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>313.2808076980544</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$376,A21,'Species'!$U$2:$U$376))</x:f>
-        <x:v>128549.820202301</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.474821131090595</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>298.4153309761828</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>122450.0071500444</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>6099.813052256592</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.049814721895297</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.049814721895297</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>921.6152375855999</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.3588614835563195</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>228.48699372524214</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>921.6152375855999</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>335.36091685359645</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$376,A22,'Species'!$U$2:$U$376))</x:f>
-        <x:v>309073.7310629519</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.3588614835563195</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>228.48699372524214</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>210577.0950073085</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>98496.63605564341</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.467746200279878</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.46774620027987796</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>59943.1922695257</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.118842260059255</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>131.47472166020523</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>59943.1922695257</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>134.53064597873788</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$376,A23,'Species'!$U$2:$U$376))</x:f>
-        <x:v>8064196.37804698</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.118842260059255</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>131.47472166020523</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>7881014.519060058</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>183181.85898692254</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0232434363042857</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.02324343630428561</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>31.7162839158</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.1360019930951046</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>136.77351024885925</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>31.7162839158</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>140.18705083616024</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$376,A24,'Species'!$U$2:$U$376))</x:f>
-        <x:v>4446.212305638345</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.1360019930951046</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>136.77351024885925</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>4337.947483213401</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>108.26482242494421</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.024957614826804</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.02495761482680408</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>1714.7586506334999</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.643769363532185</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>440.3209645126116</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>1714.7586506334999</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>597.2343933105358</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$376,A25,'Species'!$U$2:$U$376))</x:f>
-        <x:v>1024112.8423850914</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.643769363532185</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>440.3209645126116</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>755044.1829532871</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>269068.6594318042</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.3563614759329268</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.3563614759329268</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>647.6111878366</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.7773794321966747</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>598.9346407153454</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>647.6111878366</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>607.3146184392149</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$376,A26,'Species'!$U$2:$U$376))</x:f>
-        <x:v>393303.74143795145</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.7773794321966747</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>598.9346407153454</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>387876.7741101521</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>5426.967327799357</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0139914727821733</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.013991472782173255</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>1113.1795446400997</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>3.8903762409728406</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>776.9198917317742</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>1113.1795446400997</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>822.9570700444444</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$376,A27,'Species'!$U$2:$U$376))</x:f>
-        <x:v>916098.9764904253</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>3.8903762409728406</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>776.9198917317742</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>864851.331299812</x:v>
       </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>51247.645190613344</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.059256017000739</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.05925601700073892</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G27">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O27">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0b892dca21d4b5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3103c97dee774877"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28226,7 +26742,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -28325,7 +26841,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>161337945.0867266</x:v>
+        <x:v>126841222.70377925</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28339,7 +26855,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>161337945.08672658</x:v>
+        <x:v>139703638.27953878</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28353,7 +26869,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-34496722.382947326</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28367,7 +26883,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-21634306.807187796</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28378,9 +26894,9 @@
         <x:v>EEZ_962</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -28392,47 +26908,19 @@
         <x:v>EEZ_962</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_962</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_962</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R046c8902cbdf4b99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bc289438c384de6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28479,7 +26967,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
